--- a/docs/ejemplos/Ejemplo_Clinica_Libro_con_formulas.xlsx
+++ b/docs/ejemplos/Ejemplo_Clinica_Libro_con_formulas.xlsx
@@ -799,7 +799,7 @@
         <v>Fecha de exportación:</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>25/10/2026, 22:06:38</v>
+        <v>25/10/2026, 23:01:53</v>
       </c>
     </row>
     <row r="8">
@@ -8002,7 +8002,7 @@
     </row>
     <row r="2">
       <c r="A2" s="8" t="str">
-        <v>FCFF = UDI + intereses devengados + depreciación − CAPEX de ampliaciones + recuperación del capital de trabajo (año 0: −inversión total). FCFE = FCFF − interés pagado + desembolso − amortización. Recuperación por interpolación lineal del acumulado.</v>
+        <v>FCFF = UDI + (interés devengado − escudo fiscal) + depreciación − CAPEX de ampliaciones + recuperación del capital de trabajo (año 0: −inversión total). FCFE = FCFF − interés pagado + escudo fiscal + desembolso − amortización. Recuperación por interpolación lineal del acumulado. El escudo se deriva de la regla de impuestos activa (regla plana: interés × tasa).</v>
       </c>
     </row>
     <row r="3">
@@ -10119,7 +10119,7 @@
         <v>Plazo para alcanzar los niveles previstos</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>Crecimiento de la demanda del 5 % anual desde el año 1 (supuesto ilustrativo); la ampliación de gabinetes del año 8 sostiene el crecimiento posterior.</v>
+        <v>Crecimiento de la demanda del 5 % anual desde el año 1 (supuesto ilustrativo); la ampliación de gabinetes programada en la tabla de recursos operativos (escenario B) sostiene el crecimiento posterior: el año de entrada, el CAPEX y la depreciación correspondiente se derivan del dato estructurado de la ampliación, no de este texto.</v>
       </c>
     </row>
     <row r="14">
@@ -12337,7 +12337,7 @@
         <v>FINANCIACION_ANO0</v>
       </c>
       <c r="C4" s="2" t="str">
-        <v>Los gastos de la fase de montaje del año 0 (0,8 kUSD: nómina de montaje y otros costos no capitalizables) NO están incluidos en la inversión total y quedan SIN cobertura: las fuentes declaradas cubren la inversión total, pero la necesidad total del arranque (inversión + gastos del año 0) excede la financiación disponible en 0,8 kUSD. Financie esa brecha (mayor capital de trabajo o aporte adicional) o declárela expresamente como supuesto pendiente.</v>
+        <v>Los gastos de la fase de montaje del año 0 — salidas de caja explícitas no capitalizables y NO incluidas en la inversión total (nómina de montaje 0,8: total 0,8 kUSD) — quedan SIN cobertura: las fuentes declaradas cubren la inversión total (1.480,0 kUSD), pero la necesidad total del arranque (inversión + salidas de caja netas del año 0 = 1.480,8 kUSD) excede la financiación disponible (1.480,0 kUSD) en 0,8 kUSD. Financie esa brecha (mayor capital de trabajo o aporte adicional) o declárela expresamente como supuesto pendiente. El gasto NO se deduce del resultado contable después de impuestos del año 0.</v>
       </c>
       <c r="D4" s="2" t="str">
         <v>financiero</v>
@@ -12803,13 +12803,13 @@
         <v>CUP/USD</v>
       </c>
       <c r="E4" s="2" t="str">
-        <v>Conversión CUP → USD aplicada a los salarios y a las inversiones expresadas en CUP. Finalidad: expresar en miles de USD las partidas en CUP del estado de resultados, la inversión y los beneficios al país. Valor por defecto: 743 CUP/USD, tasa ilustrativa PENDIENTE DE VALIDACIÓN OFICIAL: antes de un uso oficial debe sustituirse por la tasa vigente y documentarse la fecha de referencia y la fuente oficial.</v>
+        <v>Conversión CUP → USD aplicada a los salarios y a las inversiones expresadas en CUP. Finalidad: expresar en miles de USD las partidas en CUP del estado de resultados, la inversión y los beneficios al país. Valor por defecto: 743 CUP/USD, tasa ilustrativa PENDIENTE DE VALIDACIÓN OFICIAL: antes de un uso oficial debe sustituirse por la tasa vigente y documentarse la fecha de referencia y la fuente oficial. La fecha de referencia indica el CORTE del supuesto ilustrativo (no una cotización observada) y no puede ser posterior a la fecha del documento: una cotización futura no se presenta como dato observado.</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>Supuesto de demostración editable (743 CUP/USD, tasa ilustrativa pendiente de validación oficial). [SUPUESTO DEMOSTRATIVO]</v>
+        <v>Supuesto de demostración editable (743 CUP/USD, tasa ilustrativa pendiente de validación oficial; fecha de corte del supuesto: 2026-10-25). [SUPUESTO DEMOSTRATIVO]</v>
       </c>
       <c r="G4" s="2" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-25</v>
       </c>
     </row>
     <row r="5">
@@ -12906,10 +12906,10 @@
         <v>%</v>
       </c>
       <c r="E9" s="2" t="str">
-        <v>Crecimiento anual aplicado al canon, los servicios públicos, otros gastos fijos, aranceles, otros impuestos y royalties. Valor 0 % (por defecto) = contratos nominales a valores fijos: HIPÓTESIS deliberada y conservadora que debe declararse y validarse con los contratos reales. Afecta el estado de resultados y la caja (ambos).</v>
+        <v>Crecimiento anual aplicado al canon, los servicios públicos, otros gastos fijos, aranceles, otros impuestos y royalties. Valor 0 % (por defecto) = HIPÓTESIS DE GASTOS NOMINALES CONSTANTES: cada partida fija permanece a su valor nominal inicial durante todo el horizonte. La hipótesis solo es válida si los contratos reales fijan importes nominales por todo el período (verificación contractual PENDIENTE, no una regla del modelo); no se califica automáticamente de conservadora: si los contratos efectivamente se indexan, mantener 0 % SUBESTIMA los costos y SOBREESTIMA el resultado, y el sentido del sesgo depende de cada partida. Con un valor &gt; 0 el informe presenta la sensibilidad de resultados frente a la indexación. Afecta el estado de resultados y la caja (ambos).</v>
       </c>
       <c r="F9" s="2" t="str">
-        <v>Regla explícita documentada: 0 % = partidas nominales constantes. Edítela solo con el sustento contractual correspondiente.</v>
+        <v>Hipótesis de gastos nominales constantes, sujeta a prueba contractual: edítela solo con el sustento contractual correspondiente y declare la vigencia pactada de cada contrato.</v>
       </c>
     </row>
     <row r="10">
@@ -13077,7 +13077,7 @@
         <v>pct_reserva_legal</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>Reserva sobre la utilidad distribuible</v>
+        <v>Reserva sobre la base distribuible acumulada</v>
       </c>
       <c r="C18" s="17">
         <v>0.1</v>
@@ -13086,10 +13086,10 @@
         <v>%</v>
       </c>
       <c r="E18" s="2" t="str">
-        <v>Fracción de la base distribuible que se retiene como reserva antes de calcular los dividendos propuestos. Supuesto de demostración: la reserva legalmente exigible debe validarse.</v>
+        <v>Fracción de la base distribuible que se retiene como reserva antes de calcular los dividendos propuestos. BASE MATEMÁTICA EXACTA: base_t = MAX(0, UDI del año t + saldo acumulable de ejercicios anteriores — utilidades retenidas netas de pérdidas, de reservas ya constituidas y de repartos ya pagados —); reserva_t = pct_reserva_legal × base_t. La reserva NO se calcula solo sobre la utilidad del año: la base incluye el saldo acumulado de ejercicios anteriores. Supuesto PENDIENTE DE VALIDACIÓN JURÍDICA: la exigencia legal de constituir reservas, su porcentaje y su base exacta deben confirmarse con la normativa societaria aplicable y con la política deseada por el propietario.</v>
       </c>
       <c r="F18" s="2" t="str">
-        <v>Supuesto de demostración editable. Validar la reserva exigible para la modalidad del negocio. [SUPUESTO DEMOSTRATIVO]</v>
+        <v>Supuesto de demostración editable (reserva del 10 % sobre la base distribuible acumulada, no sobre la utilidad aislada del ejercicio). Validación jurídica pendiente. [SUPUESTO DEMOSTRATIVO]</v>
       </c>
     </row>
     <row r="19">

--- a/docs/ejemplos/Ejemplo_Clinica_Libro_con_formulas.xlsx
+++ b/docs/ejemplos/Ejemplo_Clinica_Libro_con_formulas.xlsx
@@ -58,7 +58,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <numFmts count="11">
+  <numFmts count="12">
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
@@ -68,8 +68,9 @@
     <numFmt numFmtId="171" formatCode="0.0"/>
     <numFmt numFmtId="172" formatCode="#,##0.0"/>
     <numFmt numFmtId="173" formatCode="0.0%"/>
-    <numFmt numFmtId="174" formatCode="0.0000"/>
-    <numFmt numFmtId="175" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="#,##0.0"/>
+    <numFmt numFmtId="175" formatCode="0.0000"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -381,7 +382,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -412,12 +413,13 @@
     <xf numFmtId="173" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="13" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="175" fontId="14" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="14" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -799,7 +801,7 @@
         <v>Fecha de exportación:</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>25/10/2026, 23:01:53</v>
+        <v>26/10/2026, 0:40:10</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +942,7 @@
       <c r="D4" s="19">
         <v>6</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>96000</v>
       </c>
       <c r="F4" s="14">
@@ -965,7 +967,7 @@
       <c r="D5" s="19">
         <v>3</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <v>312000</v>
       </c>
       <c r="F5" s="14">
@@ -990,7 +992,7 @@
       <c r="D6" s="19">
         <v>12</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>264000</v>
       </c>
       <c r="F6" s="14">
@@ -1015,7 +1017,7 @@
       <c r="D7" s="19">
         <v>6</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <v>168000</v>
       </c>
       <c r="F7" s="14">
@@ -1040,7 +1042,7 @@
       <c r="D8" s="19">
         <v>5</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <v>120000</v>
       </c>
       <c r="F8" s="14">
@@ -1065,7 +1067,7 @@
       <c r="D9" s="19">
         <v>1</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <v>9600000</v>
       </c>
       <c r="F9" s="14">
@@ -1090,7 +1092,7 @@
       <c r="D10" s="19">
         <v>3</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <v>312000</v>
       </c>
       <c r="F10" s="14">
@@ -1115,7 +1117,7 @@
       <c r="D11" s="19">
         <v>12</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <v>264000</v>
       </c>
       <c r="F11" s="14">
@@ -1140,7 +1142,7 @@
       <c r="D12" s="19">
         <v>6</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <v>168000</v>
       </c>
       <c r="F12" s="14">
@@ -1165,7 +1167,7 @@
       <c r="D13" s="19">
         <v>5</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <v>120000</v>
       </c>
       <c r="F13" s="14">
@@ -1190,7 +1192,7 @@
       <c r="D14" s="19">
         <v>1</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <v>9600000</v>
       </c>
       <c r="F14" s="14">
@@ -1215,7 +1217,7 @@
       <c r="D15" s="19">
         <v>3</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <v>312000</v>
       </c>
       <c r="F15" s="14">
@@ -1240,7 +1242,7 @@
       <c r="D16" s="19">
         <v>12</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <v>264000</v>
       </c>
       <c r="F16" s="14">
@@ -1265,7 +1267,7 @@
       <c r="D17" s="19">
         <v>6</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <v>168000</v>
       </c>
       <c r="F17" s="14">
@@ -1290,7 +1292,7 @@
       <c r="D18" s="19">
         <v>5</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <v>120000</v>
       </c>
       <c r="F18" s="14">
@@ -1315,7 +1317,7 @@
       <c r="D19" s="19">
         <v>1</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="27">
         <v>9600000</v>
       </c>
       <c r="F19" s="14">
@@ -1340,7 +1342,7 @@
       <c r="D20" s="19">
         <v>3</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <v>312000</v>
       </c>
       <c r="F20" s="14">
@@ -1365,7 +1367,7 @@
       <c r="D21" s="19">
         <v>12</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <v>264000</v>
       </c>
       <c r="F21" s="14">
@@ -1390,7 +1392,7 @@
       <c r="D22" s="19">
         <v>6</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <v>168000</v>
       </c>
       <c r="F22" s="14">
@@ -1415,7 +1417,7 @@
       <c r="D23" s="19">
         <v>5</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="27">
         <v>120000</v>
       </c>
       <c r="F23" s="14">
@@ -1440,7 +1442,7 @@
       <c r="D24" s="19">
         <v>1</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <v>9600000</v>
       </c>
       <c r="F24" s="14">
@@ -1465,7 +1467,7 @@
       <c r="D25" s="19">
         <v>3</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <v>312000</v>
       </c>
       <c r="F25" s="14">
@@ -1490,7 +1492,7 @@
       <c r="D26" s="19">
         <v>12</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="27">
         <v>264000</v>
       </c>
       <c r="F26" s="14">
@@ -1515,7 +1517,7 @@
       <c r="D27" s="19">
         <v>6</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="27">
         <v>168000</v>
       </c>
       <c r="F27" s="14">
@@ -1540,7 +1542,7 @@
       <c r="D28" s="19">
         <v>5</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="27">
         <v>120000</v>
       </c>
       <c r="F28" s="14">
@@ -1565,7 +1567,7 @@
       <c r="D29" s="19">
         <v>1</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="27">
         <v>9600000</v>
       </c>
       <c r="F29" s="14">
@@ -1590,7 +1592,7 @@
       <c r="D30" s="19">
         <v>3</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="27">
         <v>312000</v>
       </c>
       <c r="F30" s="14">
@@ -1615,7 +1617,7 @@
       <c r="D31" s="19">
         <v>12</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="27">
         <v>264000</v>
       </c>
       <c r="F31" s="14">
@@ -1640,7 +1642,7 @@
       <c r="D32" s="19">
         <v>6</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="27">
         <v>168000</v>
       </c>
       <c r="F32" s="14">
@@ -1665,7 +1667,7 @@
       <c r="D33" s="19">
         <v>5</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="27">
         <v>120000</v>
       </c>
       <c r="F33" s="14">
@@ -1690,7 +1692,7 @@
       <c r="D34" s="19">
         <v>1</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="27">
         <v>9600000</v>
       </c>
       <c r="F34" s="14">
@@ -1715,7 +1717,7 @@
       <c r="D35" s="19">
         <v>3</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="27">
         <v>312000</v>
       </c>
       <c r="F35" s="14">
@@ -1740,7 +1742,7 @@
       <c r="D36" s="19">
         <v>12</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="27">
         <v>264000</v>
       </c>
       <c r="F36" s="14">
@@ -1765,7 +1767,7 @@
       <c r="D37" s="19">
         <v>6</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="27">
         <v>168000</v>
       </c>
       <c r="F37" s="14">
@@ -1790,7 +1792,7 @@
       <c r="D38" s="19">
         <v>5</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="27">
         <v>120000</v>
       </c>
       <c r="F38" s="14">
@@ -1815,7 +1817,7 @@
       <c r="D39" s="19">
         <v>1</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="27">
         <v>9600000</v>
       </c>
       <c r="F39" s="14">
@@ -1840,7 +1842,7 @@
       <c r="D40" s="19">
         <v>3</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="27">
         <v>312000</v>
       </c>
       <c r="F40" s="14">
@@ -1865,7 +1867,7 @@
       <c r="D41" s="19">
         <v>12</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="27">
         <v>264000</v>
       </c>
       <c r="F41" s="14">
@@ -1890,7 +1892,7 @@
       <c r="D42" s="19">
         <v>6</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="27">
         <v>168000</v>
       </c>
       <c r="F42" s="14">
@@ -1915,7 +1917,7 @@
       <c r="D43" s="19">
         <v>5</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="27">
         <v>120000</v>
       </c>
       <c r="F43" s="14">
@@ -1940,7 +1942,7 @@
       <c r="D44" s="19">
         <v>1</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="27">
         <v>9600000</v>
       </c>
       <c r="F44" s="14">
@@ -1965,7 +1967,7 @@
       <c r="D45" s="19">
         <v>3</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="27">
         <v>312000</v>
       </c>
       <c r="F45" s="14">
@@ -1990,7 +1992,7 @@
       <c r="D46" s="19">
         <v>12</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="27">
         <v>264000</v>
       </c>
       <c r="F46" s="14">
@@ -2015,7 +2017,7 @@
       <c r="D47" s="19">
         <v>6</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="27">
         <v>168000</v>
       </c>
       <c r="F47" s="14">
@@ -2040,7 +2042,7 @@
       <c r="D48" s="19">
         <v>5</v>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="27">
         <v>120000</v>
       </c>
       <c r="F48" s="14">
@@ -2065,7 +2067,7 @@
       <c r="D49" s="19">
         <v>1</v>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="27">
         <v>9600000</v>
       </c>
       <c r="F49" s="14">
@@ -2090,7 +2092,7 @@
       <c r="D50" s="19">
         <v>3</v>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="27">
         <v>312000</v>
       </c>
       <c r="F50" s="14">
@@ -2115,7 +2117,7 @@
       <c r="D51" s="19">
         <v>12</v>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="27">
         <v>264000</v>
       </c>
       <c r="F51" s="14">
@@ -2140,7 +2142,7 @@
       <c r="D52" s="19">
         <v>6</v>
       </c>
-      <c r="E52" s="26">
+      <c r="E52" s="27">
         <v>168000</v>
       </c>
       <c r="F52" s="14">
@@ -2165,7 +2167,7 @@
       <c r="D53" s="19">
         <v>5</v>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="27">
         <v>120000</v>
       </c>
       <c r="F53" s="14">
@@ -2190,7 +2192,7 @@
       <c r="D54" s="19">
         <v>1</v>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="27">
         <v>9600000</v>
       </c>
       <c r="F54" s="14">
@@ -5004,10 +5006,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="26" t="str">
+      <c r="A97" s="27" t="str">
         <v>Gabinetes de atención (sillones)</v>
       </c>
-      <c r="B97" s="26" t="str">
+      <c r="B97" s="27" t="str">
         <v>gabinete</v>
       </c>
       <c r="C97" s="19">
@@ -5220,47 +5222,47 @@
       <c r="B105" s="2" t="str">
         <v>Gabinetes de atención (sillones) — escala pro-rata</v>
       </c>
-      <c r="J105" s="27">
+      <c r="J105" s="28">
         <f>=IF($J104&gt;$J103,$J103/$J104,1)</f>
         <v>1</v>
       </c>
-      <c r="K105" s="27">
+      <c r="K105" s="28">
         <f>=IF($K104&gt;$K103,$K103/$K104,1)</f>
         <v>1</v>
       </c>
-      <c r="L105" s="27">
+      <c r="L105" s="28">
         <f>=IF($L104&gt;$L103,$L103/$L104,1)</f>
         <v>1</v>
       </c>
-      <c r="M105" s="27">
+      <c r="M105" s="28">
         <f>=IF($M104&gt;$M103,$M103/$M104,1)</f>
         <v>1</v>
       </c>
-      <c r="N105" s="27">
+      <c r="N105" s="28">
         <f>=IF($N104&gt;$N103,$N103/$N104,1)</f>
         <v>1</v>
       </c>
-      <c r="O105" s="27">
+      <c r="O105" s="28">
         <f>=IF($O104&gt;$O103,$O103/$O104,1)</f>
         <v>1</v>
       </c>
-      <c r="P105" s="27">
+      <c r="P105" s="28">
         <f>=IF($P104&gt;$P103,$P103/$P104,1)</f>
         <v>1</v>
       </c>
-      <c r="Q105" s="27">
+      <c r="Q105" s="28">
         <f>=IF($Q104&gt;$Q103,$Q103/$Q104,1)</f>
         <v>1</v>
       </c>
-      <c r="R105" s="27">
+      <c r="R105" s="28">
         <f>=IF($R104&gt;$R103,$R103/$R104,1)</f>
         <v>1</v>
       </c>
-      <c r="S105" s="27">
+      <c r="S105" s="28">
         <f>=IF($S104&gt;$S103,$S103/$S104,1)</f>
         <v>1</v>
       </c>
-      <c r="T105" s="27">
+      <c r="T105" s="28">
         <f>=IF($T104&gt;$T103,$T103/$T104,1)</f>
         <v>1</v>
       </c>
@@ -5416,47 +5418,47 @@
       <c r="B109" s="2" t="str">
         <v>Equipos de imagenología dental — escala pro-rata</v>
       </c>
-      <c r="J109" s="27">
+      <c r="J109" s="28">
         <f>=IF($J108&gt;$J107,$J107/$J108,1)</f>
         <v>1</v>
       </c>
-      <c r="K109" s="27">
+      <c r="K109" s="28">
         <f>=IF($K108&gt;$K107,$K107/$K108,1)</f>
         <v>1</v>
       </c>
-      <c r="L109" s="27">
+      <c r="L109" s="28">
         <f>=IF($L108&gt;$L107,$L107/$L108,1)</f>
         <v>1</v>
       </c>
-      <c r="M109" s="27">
+      <c r="M109" s="28">
         <f>=IF($M108&gt;$M107,$M107/$M108,1)</f>
         <v>1</v>
       </c>
-      <c r="N109" s="27">
+      <c r="N109" s="28">
         <f>=IF($N108&gt;$N107,$N107/$N108,1)</f>
         <v>1</v>
       </c>
-      <c r="O109" s="27">
+      <c r="O109" s="28">
         <f>=IF($O108&gt;$O107,$O107/$O108,1)</f>
         <v>1</v>
       </c>
-      <c r="P109" s="27">
+      <c r="P109" s="28">
         <f>=IF($P108&gt;$P107,$P107/$P108,1)</f>
         <v>1</v>
       </c>
-      <c r="Q109" s="27">
+      <c r="Q109" s="28">
         <f>=IF($Q108&gt;$Q107,$Q107/$Q108,1)</f>
         <v>1</v>
       </c>
-      <c r="R109" s="27">
+      <c r="R109" s="28">
         <f>=IF($R108&gt;$R107,$R107/$R108,1)</f>
         <v>1</v>
       </c>
-      <c r="S109" s="27">
+      <c r="S109" s="28">
         <f>=IF($S108&gt;$S107,$S107/$S108,1)</f>
         <v>1</v>
       </c>
-      <c r="T109" s="27">
+      <c r="T109" s="28">
         <f>=IF($T108&gt;$T107,$T107/$T108,1)</f>
         <v>1</v>
       </c>
@@ -5612,47 +5614,47 @@
       <c r="B113" s="2" t="str">
         <v>Laboratorio de prótesis — escala pro-rata</v>
       </c>
-      <c r="J113" s="27">
+      <c r="J113" s="28">
         <f>=IF($J112&gt;$J111,$J111/$J112,1)</f>
         <v>1</v>
       </c>
-      <c r="K113" s="27">
+      <c r="K113" s="28">
         <f>=IF($K112&gt;$K111,$K111/$K112,1)</f>
         <v>1</v>
       </c>
-      <c r="L113" s="27">
+      <c r="L113" s="28">
         <f>=IF($L112&gt;$L111,$L111/$L112,1)</f>
         <v>1</v>
       </c>
-      <c r="M113" s="27">
+      <c r="M113" s="28">
         <f>=IF($M112&gt;$M111,$M111/$M112,1)</f>
         <v>1</v>
       </c>
-      <c r="N113" s="27">
+      <c r="N113" s="28">
         <f>=IF($N112&gt;$N111,$N111/$N112,1)</f>
         <v>1</v>
       </c>
-      <c r="O113" s="27">
+      <c r="O113" s="28">
         <f>=IF($O112&gt;$O111,$O111/$O112,1)</f>
         <v>1</v>
       </c>
-      <c r="P113" s="27">
+      <c r="P113" s="28">
         <f>=IF($P112&gt;$P111,$P111/$P112,1)</f>
         <v>1</v>
       </c>
-      <c r="Q113" s="27">
+      <c r="Q113" s="28">
         <f>=IF($Q112&gt;$Q111,$Q111/$Q112,1)</f>
         <v>1</v>
       </c>
-      <c r="R113" s="27">
+      <c r="R113" s="28">
         <f>=IF($R112&gt;$R111,$R111/$R112,1)</f>
         <v>1</v>
       </c>
-      <c r="S113" s="27">
+      <c r="S113" s="28">
         <f>=IF($S112&gt;$S111,$S111/$S112,1)</f>
         <v>1</v>
       </c>
-      <c r="T113" s="27">
+      <c r="T113" s="28">
         <f>=IF($T112&gt;$T111,$T111/$T112,1)</f>
         <v>1</v>
       </c>
@@ -5808,47 +5810,47 @@
       <c r="B117" s="2" t="str">
         <v>Profesionales estomatológicos — escala pro-rata</v>
       </c>
-      <c r="J117" s="27">
+      <c r="J117" s="28">
         <f>=IF($J116&gt;$J115,$J115/$J116,1)</f>
         <v>1</v>
       </c>
-      <c r="K117" s="27">
+      <c r="K117" s="28">
         <f>=IF($K116&gt;$K115,$K115/$K116,1)</f>
         <v>1</v>
       </c>
-      <c r="L117" s="27">
+      <c r="L117" s="28">
         <f>=IF($L116&gt;$L115,$L115/$L116,1)</f>
         <v>1</v>
       </c>
-      <c r="M117" s="27">
+      <c r="M117" s="28">
         <f>=IF($M116&gt;$M115,$M115/$M116,1)</f>
         <v>1</v>
       </c>
-      <c r="N117" s="27">
+      <c r="N117" s="28">
         <f>=IF($N116&gt;$N115,$N115/$N116,1)</f>
         <v>1</v>
       </c>
-      <c r="O117" s="27">
+      <c r="O117" s="28">
         <f>=IF($O116&gt;$O115,$O115/$O116,1)</f>
         <v>1</v>
       </c>
-      <c r="P117" s="27">
+      <c r="P117" s="28">
         <f>=IF($P116&gt;$P115,$P115/$P116,1)</f>
         <v>1</v>
       </c>
-      <c r="Q117" s="27">
+      <c r="Q117" s="28">
         <f>=IF($Q116&gt;$Q115,$Q115/$Q116,1)</f>
         <v>1</v>
       </c>
-      <c r="R117" s="27">
+      <c r="R117" s="28">
         <f>=IF($R116&gt;$R115,$R115/$R116,1)</f>
         <v>1</v>
       </c>
-      <c r="S117" s="27">
+      <c r="S117" s="28">
         <f>=IF($S116&gt;$S115,$S115/$S116,1)</f>
         <v>1</v>
       </c>
-      <c r="T117" s="27">
+      <c r="T117" s="28">
         <f>=IF($T116&gt;$T115,$T115/$T116,1)</f>
         <v>1</v>
       </c>
@@ -5996,40 +5998,40 @@
       <c r="B3" s="12" t="str">
         <v>Unidad</v>
       </c>
-      <c r="C3" s="28">
-        <v>0</v>
-      </c>
-      <c r="D3" s="28">
-        <v>1</v>
-      </c>
-      <c r="E3" s="28">
+      <c r="C3" s="29">
+        <v>0</v>
+      </c>
+      <c r="D3" s="29">
+        <v>1</v>
+      </c>
+      <c r="E3" s="29">
         <v>2</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="29">
         <v>3</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="29">
         <v>4</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="29">
         <v>5</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="29">
         <v>6</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="29">
         <v>7</v>
       </c>
-      <c r="K3" s="28">
+      <c r="K3" s="29">
         <v>8</v>
       </c>
-      <c r="L3" s="28">
+      <c r="L3" s="29">
         <v>9</v>
       </c>
-      <c r="M3" s="28">
+      <c r="M3" s="29">
         <v>10</v>
       </c>
-      <c r="N3" s="28" t="str">
+      <c r="N3" s="29" t="str">
         <v>Total</v>
       </c>
     </row>
@@ -8006,40 +8008,40 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>Concepto</v>
       </c>
-      <c r="B3" s="28">
-        <v>0</v>
-      </c>
-      <c r="C3" s="28">
-        <v>1</v>
-      </c>
-      <c r="D3" s="28">
+      <c r="B3" s="29">
+        <v>0</v>
+      </c>
+      <c r="C3" s="29">
+        <v>1</v>
+      </c>
+      <c r="D3" s="29">
         <v>2</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="29">
         <v>3</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="29">
         <v>4</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="29">
         <v>5</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="29">
         <v>6</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="29">
         <v>7</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="29">
         <v>8</v>
       </c>
-      <c r="K3" s="28">
+      <c r="K3" s="29">
         <v>9</v>
       </c>
-      <c r="L3" s="28">
+      <c r="L3" s="29">
         <v>10</v>
       </c>
     </row>
@@ -8431,7 +8433,7 @@
       <c r="A14" s="22" t="str">
         <v>PERÍODO DE RECUPERACIÓN — INVERSIÓN TOTAL (años)</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <f>=IF(COUNT(C11:L$11)=0,"No se recupera en el horizonte",MIN(C11:L$11))</f>
         <v>3.463532275371478</v>
       </c>
@@ -8440,7 +8442,7 @@
       <c r="A15" s="8" t="str">
         <v>Método: interpolación lineal (t−1) + |acumulado anterior| / (acumulado actual − acumulado anterior); el mínimo de los cruces detectados.</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <f>=IF(COUNT(C12:L$12)=0,"No se recupera en el horizonte",MIN(C12:L$12))</f>
         <v>3.216105035737436</v>
       </c>
@@ -8579,40 +8581,40 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>Concepto</v>
       </c>
-      <c r="B3" s="28">
-        <v>0</v>
-      </c>
-      <c r="C3" s="28">
-        <v>1</v>
-      </c>
-      <c r="D3" s="28">
+      <c r="B3" s="29">
+        <v>0</v>
+      </c>
+      <c r="C3" s="29">
+        <v>1</v>
+      </c>
+      <c r="D3" s="29">
         <v>2</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="29">
         <v>3</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="29">
         <v>4</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="29">
         <v>5</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="29">
         <v>6</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="29">
         <v>7</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="29">
         <v>8</v>
       </c>
-      <c r="K3" s="28">
+      <c r="K3" s="29">
         <v>9</v>
       </c>
-      <c r="L3" s="28">
+      <c r="L3" s="29">
         <v>10</v>
       </c>
     </row>
@@ -9197,43 +9199,43 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>Concepto</v>
       </c>
-      <c r="B3" s="28">
-        <v>0</v>
-      </c>
-      <c r="C3" s="28">
-        <v>1</v>
-      </c>
-      <c r="D3" s="28">
+      <c r="B3" s="29">
+        <v>0</v>
+      </c>
+      <c r="C3" s="29">
+        <v>1</v>
+      </c>
+      <c r="D3" s="29">
         <v>2</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="29">
         <v>3</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="29">
         <v>4</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="29">
         <v>5</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="29">
         <v>6</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="29">
         <v>7</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="29">
         <v>8</v>
       </c>
-      <c r="K3" s="28">
+      <c r="K3" s="29">
         <v>9</v>
       </c>
-      <c r="L3" s="28">
+      <c r="L3" s="29">
         <v>10</v>
       </c>
-      <c r="M3" s="28" t="str">
+      <c r="M3" s="29" t="str">
         <v>Total</v>
       </c>
     </row>
@@ -9745,13 +9747,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>Categoría</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="29" t="str">
         <v>Cantidad</v>
       </c>
-      <c r="C3" s="28" t="str">
+      <c r="C3" s="29" t="str">
         <v>Salario promedio anual (CUP)</v>
       </c>
     </row>
@@ -9807,7 +9809,7 @@
       <c r="A8" s="22" t="str">
         <v>Total (operación)</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <f>=SUM(B4:B7)</f>
         <v>27</v>
       </c>
@@ -9857,16 +9859,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>Etapa</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="29" t="str">
         <v>Inicio</v>
       </c>
-      <c r="C3" s="28" t="str">
+      <c r="C3" s="29" t="str">
         <v>Fin</v>
       </c>
-      <c r="D3" s="28" t="str">
+      <c r="D3" s="29" t="str">
         <v>Observación</v>
       </c>
     </row>
@@ -9992,19 +9994,19 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>Concepto</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="29" t="str">
         <v>Unidad</v>
       </c>
-      <c r="C3" s="28" t="str">
+      <c r="C3" s="29" t="str">
         <v>Cantidad</v>
       </c>
-      <c r="D3" s="28" t="str">
+      <c r="D3" s="29" t="str">
         <v>Período</v>
       </c>
-      <c r="E3" s="28" t="str">
+      <c r="E3" s="29" t="str">
         <v>Observación</v>
       </c>
     </row>
@@ -10199,7 +10201,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>Caracterización de productos y servicios</v>
       </c>
       <c r="B3" s="2" t="str">
@@ -10207,7 +10209,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="str">
+      <c r="A4" s="29" t="str">
         <v>Requisitos regulatorios y registros</v>
       </c>
       <c r="B4" s="2" t="str">
@@ -10215,7 +10217,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="str">
+      <c r="A5" s="29" t="str">
         <v>Materias primas y materiales auxiliares</v>
       </c>
       <c r="B5" s="2" t="str">
@@ -10223,7 +10225,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="str">
+      <c r="A6" s="29" t="str">
         <v>Fuentes y ubicación de suministros</v>
       </c>
       <c r="B6" s="2" t="str">
@@ -10231,7 +10233,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="str">
+      <c r="A7" s="29" t="str">
         <v>Consumo estimado</v>
       </c>
       <c r="B7" s="2" t="str">
@@ -10239,7 +10241,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="str">
+      <c r="A8" s="29" t="str">
         <v>Demanda aparente</v>
       </c>
       <c r="B8" s="2" t="str">
@@ -10247,7 +10249,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="str">
+      <c r="A9" s="29" t="str">
         <v>Demanda solvente</v>
       </c>
       <c r="B9" s="2" t="str">
@@ -10255,7 +10257,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="str">
+      <c r="A10" s="29" t="str">
         <v>Método de estimación</v>
       </c>
       <c r="B10" s="2" t="str">
@@ -10263,7 +10265,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="str">
+      <c r="A11" s="29" t="str">
         <v>Fuentes consultadas (con fecha)</v>
       </c>
       <c r="B11" s="2" t="str">
@@ -10271,7 +10273,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="str">
+      <c r="A12" s="29" t="str">
         <v>Comercialización: exportaciones</v>
       </c>
       <c r="B12" s="2" t="str">
@@ -10279,7 +10281,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="str">
+      <c r="A13" s="29" t="str">
         <v>Comercialización: divisas</v>
       </c>
       <c r="B13" s="2" t="str">
@@ -10287,7 +10289,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="str">
+      <c r="A14" s="29" t="str">
         <v>Comercialización: moneda nacional</v>
       </c>
       <c r="B14" s="2" t="str">
@@ -10489,7 +10491,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>Elaborado por</v>
       </c>
       <c r="B3" s="2" t="str">
@@ -10497,7 +10499,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="str">
+      <c r="A4" s="29" t="str">
         <v>Cargo</v>
       </c>
       <c r="B4" s="2" t="str">
@@ -10505,7 +10507,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="str">
+      <c r="A5" s="29" t="str">
         <v>Fecha</v>
       </c>
       <c r="B5" s="2" t="str">
@@ -10513,7 +10515,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="str">
+      <c r="A6" s="29" t="str">
         <v>Declaración de responsabilidad</v>
       </c>
       <c r="B6" s="2" t="str">
@@ -10521,7 +10523,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="str">
+      <c r="A7" s="29" t="str">
         <v>Nombre del proyecto</v>
       </c>
       <c r="B7" s="2" t="str">
@@ -10529,7 +10531,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="str">
+      <c r="A8" s="29" t="str">
         <v>Denominación de la propuesta</v>
       </c>
       <c r="B8" s="2" t="str">
@@ -10537,7 +10539,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="str">
+      <c r="A9" s="29" t="str">
         <v>Modalidad de inversión</v>
       </c>
       <c r="B9" s="2" t="str">
@@ -10545,7 +10547,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="str">
+      <c r="A10" s="29" t="str">
         <v>Objeto social o contractual</v>
       </c>
       <c r="B10" s="2" t="str">
@@ -10553,7 +10555,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="str">
+      <c r="A11" s="29" t="str">
         <v>Plazo de vigencia</v>
       </c>
       <c r="B11" s="2" t="str">
@@ -10561,7 +10563,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="str">
+      <c r="A12" s="29" t="str">
         <v>Fundamentación y propuesta de valor</v>
       </c>
       <c r="B12" s="2" t="str">
@@ -10569,7 +10571,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="str">
+      <c r="A13" s="29" t="str">
         <v>Relación con objetivos de la inversión extranjera</v>
       </c>
       <c r="B13" s="2" t="str">
@@ -10577,7 +10579,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="str">
+      <c r="A14" s="29" t="str">
         <v>Relación con el PNDES</v>
       </c>
       <c r="B14" s="2" t="str">
@@ -10585,7 +10587,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="str">
+      <c r="A15" s="29" t="str">
         <v>Relación con la estrategia territorial</v>
       </c>
       <c r="B15" s="2" t="str">
@@ -10593,7 +10595,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="str">
+      <c r="A16" s="29" t="str">
         <v>Bienes y servicios</v>
       </c>
       <c r="B16" s="2" t="str">
@@ -10601,7 +10603,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="str">
+      <c r="A17" s="29" t="str">
         <v>Mercado interno</v>
       </c>
       <c r="B17" s="2" t="str">
@@ -10609,7 +10611,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="str">
+      <c r="A18" s="29" t="str">
         <v>Mercado externo</v>
       </c>
       <c r="B18" s="2" t="str">
@@ -10617,7 +10619,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="str">
+      <c r="A19" s="29" t="str">
         <v>Regla de distribución de beneficios</v>
       </c>
       <c r="B19" s="2" t="str">
@@ -10625,7 +10627,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="str">
+      <c r="A20" s="29" t="str">
         <v>Inversionista extranjero — nombre</v>
       </c>
       <c r="B20" s="2" t="str">
@@ -10633,7 +10635,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="str">
+      <c r="A21" s="29" t="str">
         <v>Inversionista extranjero — domicilio</v>
       </c>
       <c r="B21" s="2" t="str">
@@ -10641,7 +10643,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="str">
+      <c r="A22" s="29" t="str">
         <v>Inversionista extranjero — identificación fiscal</v>
       </c>
       <c r="B22" s="2" t="str">
@@ -10649,7 +10651,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="str">
+      <c r="A23" s="29" t="str">
         <v>Inversionista extranjero — experiencia</v>
       </c>
       <c r="B23" s="2" t="str">
@@ -10657,7 +10659,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="str">
+      <c r="A24" s="29" t="str">
         <v>Inversionista extranjero — vinculación con Cuba</v>
       </c>
       <c r="B24" s="2" t="str">
@@ -10665,7 +10667,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="str">
+      <c r="A25" s="29" t="str">
         <v>Inversionista nacional — nombre</v>
       </c>
       <c r="B25" s="2" t="str">
@@ -10673,7 +10675,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="str">
+      <c r="A26" s="29" t="str">
         <v>Inversionista nacional — domicilio</v>
       </c>
       <c r="B26" s="2" t="str">
@@ -10681,7 +10683,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="str">
+      <c r="A27" s="29" t="str">
         <v>Inversionista nacional — identificación fiscal</v>
       </c>
       <c r="B27" s="2" t="str">
@@ -10689,7 +10691,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="str">
+      <c r="A28" s="29" t="str">
         <v>Inversionista nacional — experiencia</v>
       </c>
       <c r="B28" s="2" t="str">
@@ -10697,7 +10699,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="str">
+      <c r="A29" s="29" t="str">
         <v>Inversionista nacional — vinculación con Cuba</v>
       </c>
       <c r="B29" s="2" t="str">
@@ -10705,7 +10707,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="str">
+      <c r="A30" s="29" t="str">
         <v>Conclusiones (marco del usuario)</v>
       </c>
       <c r="B30" s="2" t="str">
@@ -10740,31 +10742,31 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>ID</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="29" t="str">
         <v>Nombre</v>
       </c>
-      <c r="C3" s="28" t="str">
+      <c r="C3" s="29" t="str">
         <v>Categoría</v>
       </c>
-      <c r="D3" s="28" t="str">
+      <c r="D3" s="29" t="str">
         <v>Ámbito</v>
       </c>
-      <c r="E3" s="28" t="str">
+      <c r="E3" s="29" t="str">
         <v>Unidad</v>
       </c>
-      <c r="F3" s="28" t="str">
+      <c r="F3" s="29" t="str">
         <v>Habilitada</v>
       </c>
-      <c r="G3" s="28" t="str">
+      <c r="G3" s="29" t="str">
         <v>Expresión activa (motor PLANEX)</v>
       </c>
-      <c r="H3" s="28" t="str">
+      <c r="H3" s="29" t="str">
         <v>Equivalente Excel (año 1)</v>
       </c>
-      <c r="I3" s="28" t="str">
+      <c r="I3" s="29" t="str">
         <v>Estado</v>
       </c>
     </row>
@@ -12290,7 +12292,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -12307,46 +12309,46 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <v>Nivel</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="29" t="str">
         <v>Código</v>
       </c>
-      <c r="C3" s="28" t="str">
+      <c r="C3" s="29" t="str">
         <v>Hallazgo</v>
       </c>
-      <c r="D3" s="28" t="str">
+      <c r="D3" s="29" t="str">
         <v>Partida</v>
       </c>
-      <c r="E3" s="28" t="str">
+      <c r="E3" s="29" t="str">
         <v>Consecuencia</v>
       </c>
-      <c r="F3" s="28" t="str">
+      <c r="F3" s="29" t="str">
         <v>Corrección</v>
       </c>
-      <c r="G3" s="28" t="str">
+      <c r="G3" s="29" t="str">
         <v>Afecta conclusiones</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="str">
+      <c r="A4" s="32" t="str">
         <v>advertencia_importante</v>
       </c>
       <c r="B4" s="2" t="str">
         <v>FINANCIACION_ANO0</v>
       </c>
       <c r="C4" s="2" t="str">
-        <v>Los gastos de la fase de montaje del año 0 — salidas de caja explícitas no capitalizables y NO incluidas en la inversión total (nómina de montaje 0,8: total 0,8 kUSD) — quedan SIN cobertura: las fuentes declaradas cubren la inversión total (1.480,0 kUSD), pero la necesidad total del arranque (inversión + salidas de caja netas del año 0 = 1.480,8 kUSD) excede la financiación disponible (1.480,0 kUSD) en 0,8 kUSD. Financie esa brecha (mayor capital de trabajo o aporte adicional) o declárela expresamente como supuesto pendiente. El gasto NO se deduce del resultado contable después de impuestos del año 0.</v>
+        <v>Los gastos de la fase de montaje del año 0 — salidas de caja explícitas no capitalizables y NO incluidas en la inversión total (nómina de montaje 0,8: total 0,8 kUSD) — quedan SIN cobertura temporal: la necesidad total del arranque (inversión 1.480,0 + salidas netas del año 0 = 1.480,8 kUSD) excede las fuentes con desembolso efectivo en el año 0 (1.480,0 kUSD) en 0,8 kUSD. La financiación comprometida total (1.480,0 kUSD) tampoco cubre la necesidad total (1.480,8 kUSD): brecha nominal de 0,8 kUSD. Financie esa brecha (mayor capital de trabajo, aporte anticipado o crédito con desembolso en el año 0) o declárela expresamente como supuesto pendiente. El gasto NO se deduce del resultado contable después de impuestos del año 0.</v>
       </c>
       <c r="D4" s="2" t="str">
         <v>financiero</v>
       </c>
       <c r="E4" s="2" t="str">
-        <v>La necesidad total de arranque (inversión más gastos del año 0) excede la financiación declarada: el plan presenta una brecha de caja no resuelta.</v>
+        <v>La necesidad total de arranque (inversión más salidas de caja del año 0) excede las fuentes con desembolso efectivo en el año 0: el plan presenta una brecha de caja no resuelta cuando se produce.</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>Amplíe el capital de trabajo o las fuentes, o declare la brecha como supuesto pendiente de resolver.</v>
+        <v>Amplíe el capital de trabajo, antícipe aportes o el desembolso del crédito, o declare la brecha como supuesto pendiente de resolver.</v>
       </c>
       <c r="G4" s="2" t="str">
         <v>SÍ</v>
@@ -12492,22 +12494,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="str">
-        <v>informacion_pendiente</v>
+        <v>observacion_calidad</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>PENDIENTE</v>
+        <v>SUPUESTO_IMPUESTO_MISMO_PERIODO</v>
       </c>
       <c r="C11" s="2" t="str">
-        <v>Falta identificar al elaborador del plan (4.1): el campo está vacío o marcado como pendiente.</v>
+        <v>El impuesto sobre utilidades del modelo es un DEVENGADO contable (regla editable): el modelo simplificado SUPONE que se paga dentro del mismo período, sin calendario tributario. Ese supuesto se distingue expresamente de un pago verificado: con un calendario de pagos real (fracciones, diferimientos, pago al año siguiente) la tesorería proyectada y la necesidad de caja del arranque cambiarían.</v>
       </c>
       <c r="D11" s="2" t="str">
-        <v>4.1</v>
+        <v>impuesto_utilidades_k</v>
       </c>
       <c r="E11" s="2" t="str">
-        <v>El apartado no está completado sustantivamente.</v>
+        <v>La tesorería proyectada descansa en un supuesto de pago simultáneo, no en un calendario tributario verificado.</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>Complete la información o declare expresamente que está pendiente.</v>
+        <v>Documente la regla de pago tributaria aplicable (fuente y fecha) o modele el calendario de pagos si difiere del mismo período.</v>
       </c>
       <c r="G11" s="2" t="str">
         <v>No</v>
@@ -12515,22 +12517,22 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="str">
-        <v>informacion_pendiente</v>
+        <v>observacion_calidad</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>PENDIENTE</v>
+        <v>ESCUDO_FISCAL_CLASE</v>
       </c>
       <c r="C12" s="2" t="str">
-        <v>Falta la firma o identificación del elaborador (4.1).</v>
+        <v>Escudo fiscal — clasificación de la regla de impuestos activa: base directa. La regla de impuestos grava directamente la utilidad antes de intereses (referencia directa a «utilidad_antes_impuestos_k»): el escudo se calcula reevaluando la MISMA regla con la base hipotética sin intereses, respetando topes, mínimos y condiciones de su fórmula.</v>
       </c>
       <c r="D12" s="2" t="str">
-        <v>4.1</v>
+        <v>escudo fiscal</v>
       </c>
       <c r="E12" s="2" t="str">
-        <v>El apartado no está completado sustantivamente.</v>
+        <v>Clasificación documentada: la valoración de los flujos conoce qué reevalúa y qué no.</v>
       </c>
       <c r="F12" s="2" t="str">
-        <v>Complete la información o declare expresamente que está pendiente.</v>
+        <v>Mantenga la regla de impuestos reevaluable (sin dependencias circulares ni errores de dominio con la base hipotética).</v>
       </c>
       <c r="G12" s="2" t="str">
         <v>No</v>
@@ -12544,7 +12546,7 @@
         <v>PENDIENTE</v>
       </c>
       <c r="C13" s="2" t="str">
-        <v>La declaración de responsabilidad no ha sido aceptada (4.1): el documento NO está en condiciones de presentarse como definitivo.</v>
+        <v>Falta identificar al elaborador del plan (4.1): el campo está vacío o marcado como pendiente.</v>
       </c>
       <c r="D13" s="2" t="str">
         <v>4.1</v>
@@ -12564,166 +12566,212 @@
         <v>informacion_pendiente</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>REFERENCIA_HIPOTESIS</v>
+        <v>PENDIENTE</v>
       </c>
       <c r="C14" s="2" t="str">
-        <v>5 aportación(es) declaran una «referencia documental» que en realidad es una HIPÓTESIS de demostración (figuran como ficticia, ilustrativa, proforma o pendiente). Una referencia documental exigible debe identificar el documento, su emisor y su fecha, y adjuntar el soporte cuando corresponda.</v>
+        <v>Falta la firma o identificación del elaborador (4.1).</v>
       </c>
       <c r="D14" s="2" t="str">
-        <v>aportaciones</v>
+        <v>4.1</v>
       </c>
       <c r="E14" s="2" t="str">
-        <v>Los aportes no cuentan con respaldo acreditado: el plan no está en condiciones de presentarse oficialmente.</v>
+        <v>El apartado no está completado sustantivamente.</v>
       </c>
       <c r="F14" s="2" t="str">
-        <v>Sustituya las referencias hipotéticas por documentos identificables (título, emisor, fecha) o declare la ausencia de soporte.</v>
+        <v>Complete la información o declare expresamente que está pendiente.</v>
       </c>
       <c r="G14" s="2" t="str">
         <v>No</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="str">
+        <v>informacion_pendiente</v>
+      </c>
+      <c r="B15" s="2" t="str">
+        <v>PENDIENTE</v>
+      </c>
+      <c r="C15" s="2" t="str">
+        <v>La declaración de responsabilidad no ha sido aceptada (4.1): el documento NO está en condiciones de presentarse como definitivo.</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <v>4.1</v>
+      </c>
+      <c r="E15" s="2" t="str">
+        <v>El apartado no está completado sustantivamente.</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <v>Complete la información o declare expresamente que está pendiente.</v>
+      </c>
+      <c r="G15" s="2" t="str">
+        <v>No</v>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="3" t="str">
+      <c r="A16" s="2" t="str">
+        <v>informacion_pendiente</v>
+      </c>
+      <c r="B16" s="2" t="str">
+        <v>REFERENCIA_HIPOTESIS</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <v>5 aportación(es) declaran una «referencia documental» que en realidad es una HIPÓTESIS de demostración (figuran como ficticia, ilustrativa, proforma o pendiente). Una referencia documental exigible debe identificar el documento, su emisor y su fecha, y adjuntar el soporte cuando corresponda.</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <v>aportaciones</v>
+      </c>
+      <c r="E16" s="2" t="str">
+        <v>Los aportes no cuentan con respaldo acreditado: el plan no está en condiciones de presentarse oficialmente.</v>
+      </c>
+      <c r="F16" s="2" t="str">
+        <v>Sustituya las referencias hipotéticas por documentos identificables (título, emisor, fecha) o declare la ausencia de soporte.</v>
+      </c>
+      <c r="G16" s="2" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="str">
         <v>RESUMEN DE CONTROL</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="28" t="str">
+    <row r="19">
+      <c r="A19" s="29" t="str">
         <v>Dimensión</v>
       </c>
-      <c r="B17" s="28" t="str">
+      <c r="B19" s="29" t="str">
         <v>Estado</v>
       </c>
-      <c r="C17" s="28" t="str">
+      <c r="C19" s="29" t="str">
         <v>Detalle</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="str">
-        <v>Integridad aritmética</v>
-      </c>
-      <c r="B18" s="32" t="str">
-        <v>ok</v>
-      </c>
-      <c r="C18" s="2" t="str">
-        <v>Las reglas evalúan sin errores, la deuda reconcilia saldo a saldo, la depreciación no excede las bases y FCFF/FCFE cumplen la identidad algebraica.</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="str">
-        <v>Coherencia financiera y contable</v>
-      </c>
-      <c r="B19" s="33" t="str">
-        <v>deficiente</v>
-      </c>
-      <c r="C19" s="2" t="str">
-        <v>Inversión 1.480,0 kUSD vs financiación disponible 1.480,0 kUSD (conciliación del desembolso inicial incluida en el informe); recuperación simple del proyecto 3,5 años; del capital aportado 3,2 años; capacidad verificada contra los recursos operativos.</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="str">
-        <v>Evidencia y trazabilidad de los supuestos</v>
-      </c>
-      <c r="B20" s="34" t="str">
-        <v>deficiente</v>
+        <v>Integridad aritmética</v>
+      </c>
+      <c r="B20" s="33" t="str">
+        <v>ok</v>
       </c>
       <c r="C20" s="2" t="str">
-        <v>4 parámetro(s) de demostración sin validación normativa; 5 aportación(es) sin referencia documental IDENTIFICABLE (vacía o hipótesis); 0 con referencia declarada. Las referencias hipotéticas NO cuentan como fuentes validadas.</v>
+        <v>Las reglas evalúan sin errores, la deuda reconcilia saldo a saldo, la depreciación no excede las bases y FCFF/FCFE cumplen la identidad algebraica.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="str">
-        <v>Cumplimiento de la estructura metodológica</v>
+        <v>Coherencia financiera y contable</v>
       </c>
       <c r="B21" s="34" t="str">
         <v>deficiente</v>
       </c>
       <c r="C21" s="2" t="str">
-        <v>Apartados 4.1–4.12 con 4 elemento(s) pendiente(s). Pendientes: 4.1, aportaciones. La completitud formal no equivale a validación de contenido.</v>
+        <v>Inversión 1.480,0 kUSD vs financiación comprometida 1.480,0 kUSD (conciliación total) y fuentes con desembolso en el año 0 1.480,0 kUSD (conciliación temporal, incluida en el informe); recuperación simple del proyecto 3,5 años; del capital aportado 3,2 años; capacidad verificada contra los recursos operativos.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="str">
-        <v>Estado de validación normativa y comercial</v>
-      </c>
-      <c r="B22" s="31" t="str">
-        <v>aceptable</v>
+        <v>Evidencia y trazabilidad de los supuestos</v>
+      </c>
+      <c r="B22" s="35" t="str">
+        <v>deficiente</v>
       </c>
       <c r="C22" s="2" t="str">
-        <v>La aplicación NO valida el cumplimiento legal, tributario, sanitario ni de mercado: la estructura documental no equivale a validación normativa. Los requisitos regulatorios declarados están LISTADOS, no VERIFICADOS: cada autorización exige evidencia externa comprobable (número, emisor, fecha). La demanda solvente y los precios requieren fuentes con fecha.</v>
+        <v>4 parámetro(s) de demostración sin validación normativa; 5 aportación(es) sin referencia documental IDENTIFICABLE (vacía o hipótesis); 0 con referencia declarada. Las referencias hipotéticas NO cuentan como fuentes validadas.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="str">
+        <v>Cumplimiento de la estructura metodológica</v>
+      </c>
+      <c r="B23" s="35" t="str">
+        <v>deficiente</v>
+      </c>
+      <c r="C23" s="2" t="str">
+        <v>Apartados 4.1–4.12 con 4 elemento(s) pendiente(s). Pendientes: 4.1, aportaciones. La completitud formal no equivale a validación de contenido.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="str">
+        <v>Estado de validación normativa y comercial</v>
+      </c>
+      <c r="B24" s="32" t="str">
+        <v>aceptable</v>
+      </c>
+      <c r="C24" s="2" t="str">
+        <v>La aplicación NO valida el cumplimiento legal, tributario, sanitario ni de mercado: la estructura documental no equivale a validación normativa. Los requisitos regulatorios declarados están LISTADOS, no VERIFICADOS: cada autorización exige evidencia externa comprobable (número, emisor, fecha). La demanda solvente y los precios requieren fuentes con fecha.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="str">
         <v>Calidad documental</v>
       </c>
-      <c r="B23" s="31" t="str">
+      <c r="B25" s="32" t="str">
         <v>aceptable</v>
       </c>
-      <c r="C23" s="2" t="str">
+      <c r="C25" s="2" t="str">
         <v>Observaciones de calidad: 6; 0 análisis editados por revisar frente al modelo; campos obligatorios pendientes en 4.1: 3.</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="str">
-        <v>Conteo: 0 error(es) bloqueante(s), 1 advertencia(s) importante(s), 4 pendiente(s), 6 observación(es) de calidad.</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="str">
-        <v>ESTADO GENERAL DEL PLAN (DOC-002 §5): Borrador de demostración (datos ficticios). Plantilla de demostración con datos ficticios: sus cifras NO son datos reales y el informe no está en condiciones de presentarse a un cliente o inversionista.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="str">
+        <v>Conteo: 0 error(es) bloqueante(s), 1 advertencia(s) importante(s), 4 pendiente(s), 8 observación(es) de calidad.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="str">
+        <v>ESTADO GENERAL DEL PLAN (DOC-002 §5): Borrador de demostración (datos ficticios). Plantilla de demostración con datos ficticios: sus cifras NO son datos reales y el informe no está en condiciones de presentarse a un cliente o inversionista.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="str">
         <v>La completitud formal de campos NO se usa como prueba de calidad: un apartado completo de supuestos sin respaldo sigue sin estar validado. Las seis dimensiones se evalúan de forma independiente.</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="str">
+    <row r="29">
+      <c r="A29" s="4" t="str">
         <v>Clasificación de hallazgos (misión §15)</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="str">
-        <v>error_bloqueante</v>
-      </c>
-      <c r="B28" s="8" t="str">
-        <v>El cálculo es inválido, una fórmula tiene referencias rotas o existe una inconsistencia que impide interpretar el resultado.</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="str">
-        <v>advertencia_importante</v>
-      </c>
-      <c r="B29" s="8" t="str">
-        <v>Capacidad insuficiente, financiación no garantizada, recuperación no alcanzada o supuestos críticos no validados.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="str">
-        <v>informacion_pendiente</v>
+        <v>error_bloqueante</v>
       </c>
       <c r="B30" s="8" t="str">
-        <v>Falta completar un campo, adjuntar evidencia o documentar un supuesto.</v>
+        <v>El cálculo es inválido, una fórmula tiene referencias rotas o existe una inconsistencia que impide interpretar el resultado.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="str">
+        <v>advertencia_importante</v>
+      </c>
+      <c r="B31" s="8" t="str">
+        <v>Capacidad insuficiente, financiación no garantizada, recuperación no alcanzada o supuestos críticos no validados.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="str">
+        <v>informacion_pendiente</v>
+      </c>
+      <c r="B32" s="8" t="str">
+        <v>Falta completar un campo, adjuntar evidencia o documentar un supuesto.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="str">
         <v>observacion_calidad</v>
       </c>
-      <c r="B31" s="8" t="str">
+      <c r="B33" s="8" t="str">
         <v>Recomendación de mejorar la redacción, la evidencia, el análisis o la presentación.</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="str">
+    <row r="35">
+      <c r="A35" s="10" t="str">
         <v>EJEMPLO ILUSTRATIVO CON DATOS FICTICIOS.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G35"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15438,7 +15486,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:H36"/>
   <cols>
     <col min="1" max="1" width="48.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -15609,9 +15657,356 @@
         <v>Tasa, plazo, gracia, tipo de gracia y método de amortización: hoja Deuda (configuración editable) y hoja Parametros.</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="3" t="str">
+        <v>Cobertura temporal de la financiación y tesorería proyectada (por período)</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="str">
+        <v>Fuentes comprometidas para todo el proyecto: 1.480,0 kUSD. Disponibles con desembolso en el año 0: 1.480,0 kUSD. Brecha temporal del año 0: -0,8 kUSD (nominal: -0,8). Las «otras fuentes» no declaran fecha: se suponen del año 0.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="str">
+        <v>Período</v>
+      </c>
+      <c r="B22" s="12" t="str">
+        <v>Aportaciones del año</v>
+      </c>
+      <c r="C22" s="12" t="str">
+        <v>Otras fuentes</v>
+      </c>
+      <c r="D22" s="12" t="str">
+        <v>Crédito (desembolso)</v>
+      </c>
+      <c r="E22" s="12" t="str">
+        <v>Fuentes del período</v>
+      </c>
+      <c r="F22" s="12" t="str">
+        <v>Necesidades del período</v>
+      </c>
+      <c r="G22" s="12" t="str">
+        <v>Cobertura acumulada</v>
+      </c>
+      <c r="H22" s="12" t="str">
+        <v>Caja proyectada</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="str">
+        <v>Año 0 (montaje)</v>
+      </c>
+      <c r="B23" s="26">
+        <v>1180</v>
+      </c>
+      <c r="C23" s="26">
+        <v>0</v>
+      </c>
+      <c r="D23" s="26">
+        <v>300</v>
+      </c>
+      <c r="E23" s="6">
+        <f>=SUM(B23:D23)</f>
+        <v>1480</v>
+      </c>
+      <c r="F23" s="26">
+        <v>1480.7752355316286</v>
+      </c>
+      <c r="G23" s="26">
+        <v>-0.7752355316285957</v>
+      </c>
+      <c r="H23" s="26">
+        <v>-0.7752355316285957</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="str">
+        <v>Año 1</v>
+      </c>
+      <c r="B24" s="26">
+        <v>0</v>
+      </c>
+      <c r="C24" s="26">
+        <v>0</v>
+      </c>
+      <c r="D24" s="26">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6">
+        <f>=SUM(B24:D24)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="26">
+        <v>0</v>
+      </c>
+      <c r="G24" s="26">
+        <v>-0.7752355316285957</v>
+      </c>
+      <c r="H24" s="26">
+        <v>367.80659051144005</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="str">
+        <v>Año 2</v>
+      </c>
+      <c r="B25" s="26">
+        <v>0</v>
+      </c>
+      <c r="C25" s="26">
+        <v>0</v>
+      </c>
+      <c r="D25" s="26">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <f>=SUM(B25:D25)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="26">
+        <v>0</v>
+      </c>
+      <c r="G25" s="26">
+        <v>-0.7752355316285957</v>
+      </c>
+      <c r="H25" s="26">
+        <v>709.1861541066621</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="str">
+        <v>Año 3</v>
+      </c>
+      <c r="B26" s="26">
+        <v>0</v>
+      </c>
+      <c r="C26" s="26">
+        <v>0</v>
+      </c>
+      <c r="D26" s="26">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
+        <f>=SUM(B26:D26)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="26">
+        <v>-0.7752355316285957</v>
+      </c>
+      <c r="H26" s="26">
+        <v>1089.0175671792701</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="str">
+        <v>Año 4</v>
+      </c>
+      <c r="B27" s="26">
+        <v>0</v>
+      </c>
+      <c r="C27" s="26">
+        <v>0</v>
+      </c>
+      <c r="D27" s="26">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6">
+        <f>=SUM(B27:D27)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="26">
+        <v>0</v>
+      </c>
+      <c r="G27" s="26">
+        <v>-0.7752355316285957</v>
+      </c>
+      <c r="H27" s="26">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="str">
+        <v>Año 5</v>
+      </c>
+      <c r="B28" s="26">
+        <v>0</v>
+      </c>
+      <c r="C28" s="26">
+        <v>0</v>
+      </c>
+      <c r="D28" s="26">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <f>=SUM(B28:D28)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="26">
+        <v>0</v>
+      </c>
+      <c r="G28" s="26">
+        <v>-0.7752355316285957</v>
+      </c>
+      <c r="H28" s="26">
+        <v>1177.7743860151013</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="str">
+        <v>Año 6</v>
+      </c>
+      <c r="B29" s="26">
+        <v>0</v>
+      </c>
+      <c r="C29" s="26">
+        <v>0</v>
+      </c>
+      <c r="D29" s="26">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <f>=SUM(B29:D29)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="26">
+        <v>0</v>
+      </c>
+      <c r="G29" s="26">
+        <v>-0.7752355316285957</v>
+      </c>
+      <c r="H29" s="26">
+        <v>1270.4924946498547</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="str">
+        <v>Año 7</v>
+      </c>
+      <c r="B30" s="26">
+        <v>0</v>
+      </c>
+      <c r="C30" s="26">
+        <v>0</v>
+      </c>
+      <c r="D30" s="26">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6">
+        <f>=SUM(B30:D30)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="26">
+        <v>150</v>
+      </c>
+      <c r="G30" s="26">
+        <v>-150.7752355316286</v>
+      </c>
+      <c r="H30" s="26">
+        <v>1333.2702859615779</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="str">
+        <v>Año 8</v>
+      </c>
+      <c r="B31" s="26">
+        <v>0</v>
+      </c>
+      <c r="C31" s="26">
+        <v>0</v>
+      </c>
+      <c r="D31" s="26">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6">
+        <f>=SUM(B31:D31)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="26">
+        <v>0</v>
+      </c>
+      <c r="G31" s="26">
+        <v>-150.7752355316286</v>
+      </c>
+      <c r="H31" s="26">
+        <v>1576.072512645714</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="str">
+        <v>Año 9</v>
+      </c>
+      <c r="B32" s="26">
+        <v>0</v>
+      </c>
+      <c r="C32" s="26">
+        <v>0</v>
+      </c>
+      <c r="D32" s="26">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6">
+        <f>=SUM(B32:D32)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="26">
+        <v>0</v>
+      </c>
+      <c r="G32" s="26">
+        <v>-150.7752355316286</v>
+      </c>
+      <c r="H32" s="26">
+        <v>1831.2342900295337</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="str">
+        <v>Año 10</v>
+      </c>
+      <c r="B33" s="26">
+        <v>0</v>
+      </c>
+      <c r="C33" s="26">
+        <v>0</v>
+      </c>
+      <c r="D33" s="26">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6">
+        <f>=SUM(B33:D33)</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="26">
+        <v>0</v>
+      </c>
+      <c r="G33" s="26">
+        <v>-150.7752355316286</v>
+      </c>
+      <c r="H33" s="26">
+        <v>2101.862597535257</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="str">
+        <v>Control temporal:</v>
+      </c>
+      <c r="B35" s="25" t="str">
+        <f>=IF(MIN(H23:H33)&lt;-0.05,"DÉFICIT TEMPORAL","OK")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="str">
+        <v>Necesidades: año 0 = inversión total + salidas de caja no capitalizables del arranque (inventario: nómina de montaje + interés pagado + impuesto devengado − ingresos explícitos); años posteriores = CAPEX de ampliaciones. El impuesto se toma como devengado pagado en el mismo período (supuesto del modelo simplificado).</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H36"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15732,10 +16127,10 @@
       <c r="C4" s="16">
         <v>25</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <v>400</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>0</v>
       </c>
       <c r="F4" s="16">
@@ -15810,10 +16205,10 @@
       <c r="C5" s="16">
         <v>35</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <v>160</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <v>0</v>
       </c>
       <c r="F5" s="16">
@@ -15888,10 +16283,10 @@
       <c r="C6" s="16">
         <v>60</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <v>220</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>0</v>
       </c>
       <c r="F6" s="16">
@@ -15966,10 +16361,10 @@
       <c r="C7" s="16">
         <v>150</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="27">
         <v>70</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <v>0</v>
       </c>
       <c r="F7" s="16">
@@ -16044,10 +16439,10 @@
       <c r="C8" s="16">
         <v>120</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <v>60</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <v>0</v>
       </c>
       <c r="F8" s="16">
@@ -16122,10 +16517,10 @@
       <c r="C9" s="16">
         <v>180</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="27">
         <v>35</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <v>0</v>
       </c>
       <c r="F9" s="16">
@@ -16200,10 +16595,10 @@
       <c r="C10" s="16">
         <v>400</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <v>28</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <v>0</v>
       </c>
       <c r="F10" s="16">
@@ -16278,10 +16673,10 @@
       <c r="C11" s="16">
         <v>1200</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <v>9</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <v>0</v>
       </c>
       <c r="F11" s="16">
@@ -16356,10 +16751,10 @@
       <c r="C12" s="16">
         <v>45</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <v>130</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <v>0</v>
       </c>
       <c r="F12" s="16">
@@ -16434,10 +16829,10 @@
       <c r="C13" s="16">
         <v>25</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <v>400</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <v>0</v>
       </c>
       <c r="F13" s="16">
@@ -16512,10 +16907,10 @@
       <c r="C14" s="16">
         <v>35</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <v>160</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <v>0</v>
       </c>
       <c r="F14" s="16">
@@ -16590,10 +16985,10 @@
       <c r="C15" s="16">
         <v>60</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <v>220</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <v>0</v>
       </c>
       <c r="F15" s="16">
@@ -16668,10 +17063,10 @@
       <c r="C16" s="16">
         <v>150</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
         <v>70</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <v>0</v>
       </c>
       <c r="F16" s="16">
@@ -16746,10 +17141,10 @@
       <c r="C17" s="16">
         <v>120</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <v>60</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <v>0</v>
       </c>
       <c r="F17" s="16">
@@ -16824,10 +17219,10 @@
       <c r="C18" s="16">
         <v>180</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="27">
         <v>35</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <v>0</v>
       </c>
       <c r="F18" s="16">
@@ -16902,10 +17297,10 @@
       <c r="C19" s="16">
         <v>400</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="27">
         <v>28</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="27">
         <v>0</v>
       </c>
       <c r="F19" s="16">
@@ -16980,10 +17375,10 @@
       <c r="C20" s="16">
         <v>1200</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <v>9</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <v>0</v>
       </c>
       <c r="F20" s="16">
@@ -17058,10 +17453,10 @@
       <c r="C21" s="16">
         <v>45</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <v>130</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <v>0</v>
       </c>
       <c r="F21" s="16">
@@ -17136,10 +17531,10 @@
       <c r="C22" s="16">
         <v>25</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <v>400</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <v>0</v>
       </c>
       <c r="F22" s="16">
@@ -17214,10 +17609,10 @@
       <c r="C23" s="16">
         <v>35</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="27">
         <v>160</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="27">
         <v>0</v>
       </c>
       <c r="F23" s="16">
@@ -17292,10 +17687,10 @@
       <c r="C24" s="16">
         <v>60</v>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="27">
         <v>220</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <v>0</v>
       </c>
       <c r="F24" s="16">
@@ -17370,10 +17765,10 @@
       <c r="C25" s="16">
         <v>150</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <v>70</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <v>0</v>
       </c>
       <c r="F25" s="16">
@@ -17448,10 +17843,10 @@
       <c r="C26" s="16">
         <v>120</v>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="27">
         <v>60</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="27">
         <v>0</v>
       </c>
       <c r="F26" s="16">
@@ -17526,10 +17921,10 @@
       <c r="C27" s="16">
         <v>180</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="27">
         <v>35</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="27">
         <v>0</v>
       </c>
       <c r="F27" s="16">
@@ -17604,10 +17999,10 @@
       <c r="C28" s="16">
         <v>400</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D28" s="27">
         <v>28</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="27">
         <v>0</v>
       </c>
       <c r="F28" s="16">
@@ -17682,10 +18077,10 @@
       <c r="C29" s="16">
         <v>1200</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="27">
         <v>9</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="27">
         <v>0</v>
       </c>
       <c r="F29" s="16">
@@ -17760,10 +18155,10 @@
       <c r="C30" s="16">
         <v>45</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="27">
         <v>130</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="27">
         <v>0</v>
       </c>
       <c r="F30" s="16">
@@ -17838,10 +18233,10 @@
       <c r="C31" s="16">
         <v>25</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="27">
         <v>400</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="27">
         <v>0</v>
       </c>
       <c r="F31" s="16">
@@ -17916,10 +18311,10 @@
       <c r="C32" s="16">
         <v>35</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="27">
         <v>160</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="27">
         <v>0</v>
       </c>
       <c r="F32" s="16">
@@ -17994,10 +18389,10 @@
       <c r="C33" s="16">
         <v>60</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="27">
         <v>220</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="27">
         <v>0</v>
       </c>
       <c r="F33" s="16">
@@ -18072,10 +18467,10 @@
       <c r="C34" s="16">
         <v>150</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="27">
         <v>70</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="27">
         <v>0</v>
       </c>
       <c r="F34" s="16">
@@ -18150,10 +18545,10 @@
       <c r="C35" s="16">
         <v>120</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="27">
         <v>60</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="27">
         <v>0</v>
       </c>
       <c r="F35" s="16">
@@ -18228,10 +18623,10 @@
       <c r="C36" s="16">
         <v>180</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="27">
         <v>35</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="27">
         <v>0</v>
       </c>
       <c r="F36" s="16">
@@ -18306,10 +18701,10 @@
       <c r="C37" s="16">
         <v>400</v>
       </c>
-      <c r="D37" s="26">
+      <c r="D37" s="27">
         <v>28</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37" s="27">
         <v>0</v>
       </c>
       <c r="F37" s="16">
@@ -18384,10 +18779,10 @@
       <c r="C38" s="16">
         <v>1200</v>
       </c>
-      <c r="D38" s="26">
+      <c r="D38" s="27">
         <v>9</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="27">
         <v>0</v>
       </c>
       <c r="F38" s="16">
@@ -18462,10 +18857,10 @@
       <c r="C39" s="16">
         <v>45</v>
       </c>
-      <c r="D39" s="26">
+      <c r="D39" s="27">
         <v>130</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="27">
         <v>0</v>
       </c>
       <c r="F39" s="16">
@@ -18540,10 +18935,10 @@
       <c r="C40" s="16">
         <v>25</v>
       </c>
-      <c r="D40" s="26">
+      <c r="D40" s="27">
         <v>400</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="27">
         <v>0</v>
       </c>
       <c r="F40" s="16">
@@ -18618,10 +19013,10 @@
       <c r="C41" s="16">
         <v>35</v>
       </c>
-      <c r="D41" s="26">
+      <c r="D41" s="27">
         <v>160</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="27">
         <v>0</v>
       </c>
       <c r="F41" s="16">
@@ -18696,10 +19091,10 @@
       <c r="C42" s="16">
         <v>60</v>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="27">
         <v>220</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="27">
         <v>0</v>
       </c>
       <c r="F42" s="16">
@@ -18774,10 +19169,10 @@
       <c r="C43" s="16">
         <v>150</v>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="27">
         <v>70</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="27">
         <v>0</v>
       </c>
       <c r="F43" s="16">
@@ -18852,10 +19247,10 @@
       <c r="C44" s="16">
         <v>120</v>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="27">
         <v>60</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="27">
         <v>0</v>
       </c>
       <c r="F44" s="16">
@@ -18930,10 +19325,10 @@
       <c r="C45" s="16">
         <v>180</v>
       </c>
-      <c r="D45" s="26">
+      <c r="D45" s="27">
         <v>35</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="27">
         <v>0</v>
       </c>
       <c r="F45" s="16">
@@ -19008,10 +19403,10 @@
       <c r="C46" s="16">
         <v>400</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="27">
         <v>28</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="27">
         <v>0</v>
       </c>
       <c r="F46" s="16">
@@ -19086,10 +19481,10 @@
       <c r="C47" s="16">
         <v>1200</v>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="27">
         <v>9</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="27">
         <v>0</v>
       </c>
       <c r="F47" s="16">
@@ -19164,10 +19559,10 @@
       <c r="C48" s="16">
         <v>45</v>
       </c>
-      <c r="D48" s="26">
+      <c r="D48" s="27">
         <v>130</v>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="27">
         <v>0</v>
       </c>
       <c r="F48" s="16">
@@ -19242,10 +19637,10 @@
       <c r="C49" s="16">
         <v>25</v>
       </c>
-      <c r="D49" s="26">
+      <c r="D49" s="27">
         <v>400</v>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="27">
         <v>0</v>
       </c>
       <c r="F49" s="16">
@@ -19320,10 +19715,10 @@
       <c r="C50" s="16">
         <v>35</v>
       </c>
-      <c r="D50" s="26">
+      <c r="D50" s="27">
         <v>160</v>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="27">
         <v>0</v>
       </c>
       <c r="F50" s="16">
@@ -19398,10 +19793,10 @@
       <c r="C51" s="16">
         <v>60</v>
       </c>
-      <c r="D51" s="26">
+      <c r="D51" s="27">
         <v>220</v>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="27">
         <v>0</v>
       </c>
       <c r="F51" s="16">
@@ -19476,10 +19871,10 @@
       <c r="C52" s="16">
         <v>150</v>
       </c>
-      <c r="D52" s="26">
+      <c r="D52" s="27">
         <v>70</v>
       </c>
-      <c r="E52" s="26">
+      <c r="E52" s="27">
         <v>0</v>
       </c>
       <c r="F52" s="16">
@@ -19554,10 +19949,10 @@
       <c r="C53" s="16">
         <v>120</v>
       </c>
-      <c r="D53" s="26">
+      <c r="D53" s="27">
         <v>60</v>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="27">
         <v>0</v>
       </c>
       <c r="F53" s="16">
@@ -19632,10 +20027,10 @@
       <c r="C54" s="16">
         <v>180</v>
       </c>
-      <c r="D54" s="26">
+      <c r="D54" s="27">
         <v>35</v>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="27">
         <v>0</v>
       </c>
       <c r="F54" s="16">
@@ -19710,10 +20105,10 @@
       <c r="C55" s="16">
         <v>400</v>
       </c>
-      <c r="D55" s="26">
+      <c r="D55" s="27">
         <v>28</v>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="27">
         <v>0</v>
       </c>
       <c r="F55" s="16">
@@ -19788,10 +20183,10 @@
       <c r="C56" s="16">
         <v>1200</v>
       </c>
-      <c r="D56" s="26">
+      <c r="D56" s="27">
         <v>9</v>
       </c>
-      <c r="E56" s="26">
+      <c r="E56" s="27">
         <v>0</v>
       </c>
       <c r="F56" s="16">
@@ -19866,10 +20261,10 @@
       <c r="C57" s="16">
         <v>45</v>
       </c>
-      <c r="D57" s="26">
+      <c r="D57" s="27">
         <v>130</v>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="27">
         <v>0</v>
       </c>
       <c r="F57" s="16">
@@ -19944,10 +20339,10 @@
       <c r="C58" s="16">
         <v>25</v>
       </c>
-      <c r="D58" s="26">
+      <c r="D58" s="27">
         <v>400</v>
       </c>
-      <c r="E58" s="26">
+      <c r="E58" s="27">
         <v>0</v>
       </c>
       <c r="F58" s="16">
@@ -20022,10 +20417,10 @@
       <c r="C59" s="16">
         <v>35</v>
       </c>
-      <c r="D59" s="26">
+      <c r="D59" s="27">
         <v>160</v>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="27">
         <v>0</v>
       </c>
       <c r="F59" s="16">
@@ -20100,10 +20495,10 @@
       <c r="C60" s="16">
         <v>60</v>
       </c>
-      <c r="D60" s="26">
+      <c r="D60" s="27">
         <v>220</v>
       </c>
-      <c r="E60" s="26">
+      <c r="E60" s="27">
         <v>0</v>
       </c>
       <c r="F60" s="16">
@@ -20178,10 +20573,10 @@
       <c r="C61" s="16">
         <v>150</v>
       </c>
-      <c r="D61" s="26">
+      <c r="D61" s="27">
         <v>70</v>
       </c>
-      <c r="E61" s="26">
+      <c r="E61" s="27">
         <v>0</v>
       </c>
       <c r="F61" s="16">
@@ -20256,10 +20651,10 @@
       <c r="C62" s="16">
         <v>120</v>
       </c>
-      <c r="D62" s="26">
+      <c r="D62" s="27">
         <v>60</v>
       </c>
-      <c r="E62" s="26">
+      <c r="E62" s="27">
         <v>0</v>
       </c>
       <c r="F62" s="16">
@@ -20334,10 +20729,10 @@
       <c r="C63" s="16">
         <v>180</v>
       </c>
-      <c r="D63" s="26">
+      <c r="D63" s="27">
         <v>35</v>
       </c>
-      <c r="E63" s="26">
+      <c r="E63" s="27">
         <v>0</v>
       </c>
       <c r="F63" s="16">
@@ -20412,10 +20807,10 @@
       <c r="C64" s="16">
         <v>400</v>
       </c>
-      <c r="D64" s="26">
+      <c r="D64" s="27">
         <v>28</v>
       </c>
-      <c r="E64" s="26">
+      <c r="E64" s="27">
         <v>0</v>
       </c>
       <c r="F64" s="16">
@@ -20490,10 +20885,10 @@
       <c r="C65" s="16">
         <v>1200</v>
       </c>
-      <c r="D65" s="26">
+      <c r="D65" s="27">
         <v>9</v>
       </c>
-      <c r="E65" s="26">
+      <c r="E65" s="27">
         <v>0</v>
       </c>
       <c r="F65" s="16">
@@ -20568,10 +20963,10 @@
       <c r="C66" s="16">
         <v>45</v>
       </c>
-      <c r="D66" s="26">
+      <c r="D66" s="27">
         <v>130</v>
       </c>
-      <c r="E66" s="26">
+      <c r="E66" s="27">
         <v>0</v>
       </c>
       <c r="F66" s="16">
@@ -20646,10 +21041,10 @@
       <c r="C67" s="16">
         <v>25</v>
       </c>
-      <c r="D67" s="26">
+      <c r="D67" s="27">
         <v>400</v>
       </c>
-      <c r="E67" s="26">
+      <c r="E67" s="27">
         <v>0</v>
       </c>
       <c r="F67" s="16">
@@ -20724,10 +21119,10 @@
       <c r="C68" s="16">
         <v>35</v>
       </c>
-      <c r="D68" s="26">
+      <c r="D68" s="27">
         <v>160</v>
       </c>
-      <c r="E68" s="26">
+      <c r="E68" s="27">
         <v>0</v>
       </c>
       <c r="F68" s="16">
@@ -20802,10 +21197,10 @@
       <c r="C69" s="16">
         <v>60</v>
       </c>
-      <c r="D69" s="26">
+      <c r="D69" s="27">
         <v>220</v>
       </c>
-      <c r="E69" s="26">
+      <c r="E69" s="27">
         <v>0</v>
       </c>
       <c r="F69" s="16">
@@ -20880,10 +21275,10 @@
       <c r="C70" s="16">
         <v>150</v>
       </c>
-      <c r="D70" s="26">
+      <c r="D70" s="27">
         <v>70</v>
       </c>
-      <c r="E70" s="26">
+      <c r="E70" s="27">
         <v>0</v>
       </c>
       <c r="F70" s="16">
@@ -20958,10 +21353,10 @@
       <c r="C71" s="16">
         <v>120</v>
       </c>
-      <c r="D71" s="26">
+      <c r="D71" s="27">
         <v>60</v>
       </c>
-      <c r="E71" s="26">
+      <c r="E71" s="27">
         <v>0</v>
       </c>
       <c r="F71" s="16">
@@ -21036,10 +21431,10 @@
       <c r="C72" s="16">
         <v>180</v>
       </c>
-      <c r="D72" s="26">
+      <c r="D72" s="27">
         <v>35</v>
       </c>
-      <c r="E72" s="26">
+      <c r="E72" s="27">
         <v>0</v>
       </c>
       <c r="F72" s="16">
@@ -21114,10 +21509,10 @@
       <c r="C73" s="16">
         <v>400</v>
       </c>
-      <c r="D73" s="26">
+      <c r="D73" s="27">
         <v>28</v>
       </c>
-      <c r="E73" s="26">
+      <c r="E73" s="27">
         <v>0</v>
       </c>
       <c r="F73" s="16">
@@ -21192,10 +21587,10 @@
       <c r="C74" s="16">
         <v>1200</v>
       </c>
-      <c r="D74" s="26">
+      <c r="D74" s="27">
         <v>9</v>
       </c>
-      <c r="E74" s="26">
+      <c r="E74" s="27">
         <v>0</v>
       </c>
       <c r="F74" s="16">
@@ -21270,10 +21665,10 @@
       <c r="C75" s="16">
         <v>45</v>
       </c>
-      <c r="D75" s="26">
+      <c r="D75" s="27">
         <v>130</v>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="27">
         <v>0</v>
       </c>
       <c r="F75" s="16">
@@ -21348,10 +21743,10 @@
       <c r="C76" s="16">
         <v>25</v>
       </c>
-      <c r="D76" s="26">
+      <c r="D76" s="27">
         <v>400</v>
       </c>
-      <c r="E76" s="26">
+      <c r="E76" s="27">
         <v>0</v>
       </c>
       <c r="F76" s="16">
@@ -21426,10 +21821,10 @@
       <c r="C77" s="16">
         <v>35</v>
       </c>
-      <c r="D77" s="26">
+      <c r="D77" s="27">
         <v>160</v>
       </c>
-      <c r="E77" s="26">
+      <c r="E77" s="27">
         <v>0</v>
       </c>
       <c r="F77" s="16">
@@ -21504,10 +21899,10 @@
       <c r="C78" s="16">
         <v>60</v>
       </c>
-      <c r="D78" s="26">
+      <c r="D78" s="27">
         <v>220</v>
       </c>
-      <c r="E78" s="26">
+      <c r="E78" s="27">
         <v>0</v>
       </c>
       <c r="F78" s="16">
@@ -21582,10 +21977,10 @@
       <c r="C79" s="16">
         <v>150</v>
       </c>
-      <c r="D79" s="26">
+      <c r="D79" s="27">
         <v>70</v>
       </c>
-      <c r="E79" s="26">
+      <c r="E79" s="27">
         <v>0</v>
       </c>
       <c r="F79" s="16">
@@ -21660,10 +22055,10 @@
       <c r="C80" s="16">
         <v>120</v>
       </c>
-      <c r="D80" s="26">
+      <c r="D80" s="27">
         <v>60</v>
       </c>
-      <c r="E80" s="26">
+      <c r="E80" s="27">
         <v>0</v>
       </c>
       <c r="F80" s="16">
@@ -21738,10 +22133,10 @@
       <c r="C81" s="16">
         <v>180</v>
       </c>
-      <c r="D81" s="26">
+      <c r="D81" s="27">
         <v>35</v>
       </c>
-      <c r="E81" s="26">
+      <c r="E81" s="27">
         <v>0</v>
       </c>
       <c r="F81" s="16">
@@ -21816,10 +22211,10 @@
       <c r="C82" s="16">
         <v>400</v>
       </c>
-      <c r="D82" s="26">
+      <c r="D82" s="27">
         <v>28</v>
       </c>
-      <c r="E82" s="26">
+      <c r="E82" s="27">
         <v>0</v>
       </c>
       <c r="F82" s="16">
@@ -21894,10 +22289,10 @@
       <c r="C83" s="16">
         <v>1200</v>
       </c>
-      <c r="D83" s="26">
+      <c r="D83" s="27">
         <v>9</v>
       </c>
-      <c r="E83" s="26">
+      <c r="E83" s="27">
         <v>0</v>
       </c>
       <c r="F83" s="16">
@@ -21972,10 +22367,10 @@
       <c r="C84" s="16">
         <v>45</v>
       </c>
-      <c r="D84" s="26">
+      <c r="D84" s="27">
         <v>130</v>
       </c>
-      <c r="E84" s="26">
+      <c r="E84" s="27">
         <v>0</v>
       </c>
       <c r="F84" s="16">
@@ -22050,10 +22445,10 @@
       <c r="C85" s="16">
         <v>25</v>
       </c>
-      <c r="D85" s="26">
+      <c r="D85" s="27">
         <v>400</v>
       </c>
-      <c r="E85" s="26">
+      <c r="E85" s="27">
         <v>0</v>
       </c>
       <c r="F85" s="16">
@@ -22128,10 +22523,10 @@
       <c r="C86" s="16">
         <v>35</v>
       </c>
-      <c r="D86" s="26">
+      <c r="D86" s="27">
         <v>160</v>
       </c>
-      <c r="E86" s="26">
+      <c r="E86" s="27">
         <v>0</v>
       </c>
       <c r="F86" s="16">
@@ -22206,10 +22601,10 @@
       <c r="C87" s="16">
         <v>60</v>
       </c>
-      <c r="D87" s="26">
+      <c r="D87" s="27">
         <v>220</v>
       </c>
-      <c r="E87" s="26">
+      <c r="E87" s="27">
         <v>0</v>
       </c>
       <c r="F87" s="16">
@@ -22284,10 +22679,10 @@
       <c r="C88" s="16">
         <v>150</v>
       </c>
-      <c r="D88" s="26">
+      <c r="D88" s="27">
         <v>70</v>
       </c>
-      <c r="E88" s="26">
+      <c r="E88" s="27">
         <v>0</v>
       </c>
       <c r="F88" s="16">
@@ -22362,10 +22757,10 @@
       <c r="C89" s="16">
         <v>120</v>
       </c>
-      <c r="D89" s="26">
+      <c r="D89" s="27">
         <v>60</v>
       </c>
-      <c r="E89" s="26">
+      <c r="E89" s="27">
         <v>0</v>
       </c>
       <c r="F89" s="16">
@@ -22440,10 +22835,10 @@
       <c r="C90" s="16">
         <v>180</v>
       </c>
-      <c r="D90" s="26">
+      <c r="D90" s="27">
         <v>35</v>
       </c>
-      <c r="E90" s="26">
+      <c r="E90" s="27">
         <v>0</v>
       </c>
       <c r="F90" s="16">
@@ -22518,10 +22913,10 @@
       <c r="C91" s="16">
         <v>400</v>
       </c>
-      <c r="D91" s="26">
+      <c r="D91" s="27">
         <v>28</v>
       </c>
-      <c r="E91" s="26">
+      <c r="E91" s="27">
         <v>0</v>
       </c>
       <c r="F91" s="16">
@@ -22596,10 +22991,10 @@
       <c r="C92" s="16">
         <v>1200</v>
       </c>
-      <c r="D92" s="26">
+      <c r="D92" s="27">
         <v>9</v>
       </c>
-      <c r="E92" s="26">
+      <c r="E92" s="27">
         <v>0</v>
       </c>
       <c r="F92" s="16">
@@ -22674,10 +23069,10 @@
       <c r="C93" s="16">
         <v>45</v>
       </c>
-      <c r="D93" s="26">
+      <c r="D93" s="27">
         <v>130</v>
       </c>
-      <c r="E93" s="26">
+      <c r="E93" s="27">
         <v>0</v>
       </c>
       <c r="F93" s="16">

--- a/docs/ejemplos/Ejemplo_Clinica_Libro_con_formulas.xlsx
+++ b/docs/ejemplos/Ejemplo_Clinica_Libro_con_formulas.xlsx
@@ -801,7 +801,7 @@
         <v>Fecha de exportación:</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>26/10/2026, 0:40:10</v>
+        <v>26/10/2026, 2:20:44</v>
       </c>
     </row>
     <row r="8">
@@ -12339,7 +12339,7 @@
         <v>FINANCIACION_ANO0</v>
       </c>
       <c r="C4" s="2" t="str">
-        <v>Los gastos de la fase de montaje del año 0 — salidas de caja explícitas no capitalizables y NO incluidas en la inversión total (nómina de montaje 0,8: total 0,8 kUSD) — quedan SIN cobertura temporal: la necesidad total del arranque (inversión 1.480,0 + salidas netas del año 0 = 1.480,8 kUSD) excede las fuentes con desembolso efectivo en el año 0 (1.480,0 kUSD) en 0,8 kUSD. La financiación comprometida total (1.480,0 kUSD) tampoco cubre la necesidad total (1.480,8 kUSD): brecha nominal de 0,8 kUSD. Financie esa brecha (mayor capital de trabajo, aporte anticipado o crédito con desembolso en el año 0) o declárela expresamente como supuesto pendiente. El gasto NO se deduce del resultado contable después de impuestos del año 0.</v>
+        <v>Arranque del año 0 — salidas de caja explícitas no capitalizables y NO incluidas en la inversión total (nómina de montaje 0,8: total 0,8 kUSD) — queda SIN cobertura temporal: la necesidad total del arranque (inversión 1.480,0 + salidas netas del año 0 = 1.480,8 kUSD) excede las fuentes con desembolso efectivo en el año 0 (1.480,0 kUSD) en 0,8 kUSD. La financiación comprometida total (1.480,0 kUSD) tampoco cubre la necesidad total (1.480,8 kUSD): brecha nominal de 0,8 kUSD. Financie esa brecha (mayor capital de trabajo, aporte anticipado o crédito con desembolso en el año 0) o declárela expresamente como supuesto pendiente. El gasto NO se deduce del resultado contable después de impuestos del año 0.</v>
       </c>
       <c r="D4" s="2" t="str">
         <v>financiero</v>

--- a/docs/ejemplos/Ejemplo_Clinica_Libro_con_formulas.xlsx
+++ b/docs/ejemplos/Ejemplo_Clinica_Libro_con_formulas.xlsx
@@ -801,7 +801,7 @@
         <v>Fecha de exportación:</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>26/10/2026, 2:20:44</v>
+        <v>26/10/2026, 3:39:24</v>
       </c>
     </row>
     <row r="8">
